--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>423,000원</t>
+          <t>552,000원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-52,920원</t>
+          <t>-181,920원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-33.0%</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>947,080원</t>
+          <t>818,080원</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -683,13 +683,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>118000</v>
+        <v>247000</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-118000</v>
+        <v>-247000</v>
       </c>
       <c r="H3" t="n">
         <v>-1</v>
@@ -768,25 +768,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>142000</v>
+        <v>271000</v>
       </c>
       <c r="F2" t="n">
         <v>46530</v>
       </c>
       <c r="G2" t="n">
-        <v>-95470</v>
+        <v>-224470</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6723239436619718</v>
+        <v>-0.8283025830258303</v>
       </c>
     </row>
     <row r="3">
@@ -922,13 +922,13 @@
         <v>1065080</v>
       </c>
       <c r="C3" t="n">
-        <v>118000</v>
+        <v>247000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>947080</v>
+        <v>818080</v>
       </c>
     </row>
   </sheetData>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1354,6 +1354,105 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천①</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>오릭스 vs 지바롯데(지바롯데 승) + KIA vs 키움(KIA 승)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>64000</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SSG vs NC(NC 승) + 야쿠르트 vs 히로시마(야쿠르트 승)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2.3345</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한신 vs 요미우리(오버 5.5) + 한화 vs LG(한화 +2.5 핸디캡) + 세이부 vs 소프트뱅크(세이부 승)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5.2228</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>552,000원</t>
+          <t>4,497,000원</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370,080원</t>
+          <t>4,378,772원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-181,920원</t>
+          <t>-118,228원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>818,080원</t>
+          <t>881,772원</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,6 +693,538 @@
       </c>
       <c r="H3" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>128440</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-131560</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.506</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>249000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-249000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>170000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>159960</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-10040</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.05905882352941177</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>266000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>105570</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-160430</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.6031203007518797</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E9" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>197231.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-62768.60000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2414176923076923</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E10" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>252718.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>122718.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9439876923076923</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E11" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>237244</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-22756</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.08752307692307693</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>160000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>314670.72</v>
+      </c>
+      <c r="G12" t="n">
+        <v>154670.72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9666919999999998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>358050</v>
+      </c>
+      <c r="G14" t="n">
+        <v>158050</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.79025</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>821748.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>591748.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.572820434782609</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-260000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>206340</v>
+      </c>
+      <c r="G19" t="n">
+        <v>76340</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5872307692307692</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>662814.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>352814.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.138110967741936</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>70224</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-209776</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.7492</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>493680.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>233680.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8987699999999998</v>
       </c>
     </row>
   </sheetData>
@@ -706,17 +1238,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,84 +1296,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KBO/NPB</t>
+          <t>KBO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>271000</v>
+        <v>316000</v>
       </c>
       <c r="F2" t="n">
-        <v>46530</v>
+        <v>265530</v>
       </c>
       <c r="G2" t="n">
-        <v>-224470</v>
+        <v>-50470</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8283025830258303</v>
+        <v>-0.1597151898734177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>KBO/NPB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="E3" t="n">
-        <v>251000</v>
+        <v>1490000</v>
       </c>
       <c r="F3" t="n">
-        <v>143550</v>
+        <v>1303212.2</v>
       </c>
       <c r="G3" t="n">
-        <v>-107450</v>
+        <v>-186787.8</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4280876494023904</v>
+        <v>-0.1253609395973155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2071000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2032855.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-38144.78000000003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.01841853211009176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E5" t="n">
+        <v>590000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>597174.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7174.400000000023</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01216000000000004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>30000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>180000</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>150000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -856,13 +1444,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -929,6 +1517,367 @@
       </c>
       <c r="E3" t="n">
         <v>818080</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>818080</v>
+      </c>
+      <c r="C4" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128440</v>
+      </c>
+      <c r="E4" t="n">
+        <v>686520</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>686520</v>
+      </c>
+      <c r="C5" t="n">
+        <v>249000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>437520</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>437520</v>
+      </c>
+      <c r="C6" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>159960</v>
+      </c>
+      <c r="E6" t="n">
+        <v>427480</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>427480</v>
+      </c>
+      <c r="C7" t="n">
+        <v>266000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>105570</v>
+      </c>
+      <c r="E7" t="n">
+        <v>267050</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>267050</v>
+      </c>
+      <c r="C8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>137050</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>137050</v>
+      </c>
+      <c r="C9" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>197231.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>74281.39999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>74281.39999999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>252718.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>196999.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>196999.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>237244</v>
+      </c>
+      <c r="E11" t="n">
+        <v>174243.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>174243.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>314670.72</v>
+      </c>
+      <c r="E12" t="n">
+        <v>328914.52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>328914.52</v>
+      </c>
+      <c r="C13" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>198914.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>198914.52</v>
+      </c>
+      <c r="C14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>358050</v>
+      </c>
+      <c r="E14" t="n">
+        <v>356964.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>356964.52</v>
+      </c>
+      <c r="C15" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>226964.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>226964.52</v>
+      </c>
+      <c r="C16" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>96964.52</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>96964.52</v>
+      </c>
+      <c r="C17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>821748.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>688713.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>688713.22</v>
+      </c>
+      <c r="C18" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>428713.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>428713.22</v>
+      </c>
+      <c r="C19" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>206340</v>
+      </c>
+      <c r="E19" t="n">
+        <v>505053.22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>505053.22</v>
+      </c>
+      <c r="C20" t="n">
+        <v>310000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>662814.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>857867.62</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>857867.62</v>
+      </c>
+      <c r="C21" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>70224</v>
+      </c>
+      <c r="E21" t="n">
+        <v>648091.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>648091.62</v>
+      </c>
+      <c r="C22" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>493680.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>881771.8199999999</v>
       </c>
     </row>
   </sheetData>
@@ -942,16 +1891,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,6 +2402,2613 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천①</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>샌프란시스코 vs LA에인절스(오버 7.5) + 피츠버그 vs 시카고컵스(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.0876</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>디트로이트 vs 캔자스시티(캔자스시티 +2.5 핸디캡) + 워싱턴 vs 애리조나(애리조나 승)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2.5688</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>128440</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MLB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>미네소타 vs 애슬레틱스(오버 9.5) + 밀워키 vs 콜로라도(오버 8.5) + 세인트루이스 vs 신시내티(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5.9249</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천①</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>피츠버그 vs 시카고컵스(오버 7.5) + 시카고화이트삭스 vs 휴스턴(시카고화이트삭스 -2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>86000</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5.3088</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>보스턴 vs 토론토(보스턴 -2.5 핸디캡) + 마이애미 vs 샌디에이고(마이애미 -2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10.9174</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MLB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>밀워키 vs 콜로라도(콜로라도 승) + 뉴욕메츠 vs LA다저스(뉴욕메츠 승1패(2점차+)) + 샌프란시스코 vs LA에인절스(LA에인절스 승)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>18.0992</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MLB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>워싱턴 vs 토론토(워싱턴 승) + 피츠버그 vs 애리조나(오버 8.5) + 신시내티 vs 클리블랜드(클리블랜드 승)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6.6941</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>애슬레틱스 vs 보스턴(애슬레틱스 승) + 마이애미 vs 필라델피아(마이애미 승1패(2점차+))</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>7.548</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천①</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>두산 vs 삼성(오버 8.5) + 한신 vs 요미우리(요미우리 승)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>니혼햄 vs 라쿠텐(언더 8.5) + 야쿠르트 vs 히로시마(히로시마 -2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4.964</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>세이부 vs 소프트뱅크(오버 6.5) + 오릭스 vs 지바롯데(지바롯데 승) + 한화 vs LG(한화 승)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6.357</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천① (고승률)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한신 vs 요미우리(요미우리 승) + 니혼햄 vs 라쿠텐(언더 8.5)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>107000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4.2039</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KIA vs 키움(언더 10.5) + SSG vs NC(오버 9.5)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1668</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>롯데 vs KT(롯데 승) + 두산 vs 삼성(오버 8.5) + 야쿠르트 vs 히로시마(히로시마 승1패 2점차+)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8.6394</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KBO 2폴더 추천 (유일 성립 조합)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LG vs 키움(키움 +2.5 핸디캡) + NC vs kt(오버 9.5)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.1992</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>159960</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천①</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 시애틀(언더 9.5) + 샌디에이고 vs 콜로라도(콜로라도 승)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>54000</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4.0338</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>뉴욕메츠 vs 애틀랜타(오버 7.5) + 마이애미 vs 필라델피아(마이애미 -2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>31000</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6.3882</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MLB 2폴더 추천③</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>시카고화이트삭스 vs 뉴욕양키스(오버 8.5) + 탬파베이 vs 텍사스(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.4969</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KBO 2폴더 추천① (고확률)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>삼성 vs KIA(언더 12.5) + LG vs 키움(키움 +2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>106000</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.006</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KBO 2폴더 추천②</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SSG vs 두산(언더 11.5) + 한화 vs 롯데(한화 승1패(2점차+))</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>105570</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KBO 3폴더 추천</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LG vs 키움(언더 9.5) + 한화 vs 롯데(한화 -2.5 핸디캡) + 삼성 vs KIA(1점차)</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19.2649</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KBO 승률1등 2폴더</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NC vs kt(kt +2.5 핸디캡) + 삼성 vs KIA(언더 10.5)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2.301</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KBO EV가치픽 2폴더</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NC vs kt(kt 승1패(2점차+)) + LG vs 키움(키움 승)</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>49000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>5.325</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KBO 3폴더</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화 vs 롯데(오버 9.5) + SSG vs 두산(두산 -2.5 핸디캡)</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5.0512</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MLB 1폴더</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>애슬레틱스 vs 보스턴(언더 10.5) + 시카고W vs 뉴욕양키스(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>61000</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2.8718</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MLB 2폴더</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>신시내티 vs 피츠버그(오버 9.5) + 탬파베이 vs 텍사스(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.258</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MLB 3폴더</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 시애틀(시애틀 승) + 애틀랜타 vs 워싱턴(오버 9.5) + 세인트루이스 vs 시카고컵스(시카고컵스 승1패(2점차+))</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9.1152</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KBO/NPB 1폴더</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>롯데 vs 삼성(롯데 +2.5 핸디캡) + 야쿠르트 vs 한신(언더 8.5)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2.7018</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>197231.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>요미우리 vs 요코하마(오버 5.5) + 두산 vs LG(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>49000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2.8884</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>키움 vs SSG(오버 8.5) + 세이부 vs 오릭스(세이부 승) + kt vs 한화(오버 9.5)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4.6847</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KBO/NPB 1폴더</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kt vs 한화(한화 +2.5 핸디캡) [NC vs KIA 우천취소로 단일 다리 정산]</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>요미우리 vs 요코하마(오버 5.5) + 키움 vs SSG(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2.8718</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>252718.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>두산 vs LG(오버 8.5) + 라쿠텐 vs 소프트뱅크(라쿠텐 승) + 히로시마 vs 주니치(언더 7.5)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>5.8133</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MLB 1폴더</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>시애틀 vs 미네소타(오버 7.5) + 탬파베이 vs 시카고W(시카고W +2.5)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2.3009</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MLB 2폴더</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>클리블랜드 vs 애리조나(애리조나 +2.5) + 볼티모어 vs 필라델피아(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2.3628</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MLB 3폴더</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>애틀랜타 vs 워싱턴(워싱턴 +2.5) + 시카고컵스 vs 뉴욕양키스(오버 6.5) + 신시내티 vs 피츠버그(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4.7266</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MLB 1폴더</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>클리블랜드 vs 애리조나(애리조나 +2.5) + 콜로라도 vs 캔자스시티(언더 12.5)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>56000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2.1168</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MLB 2폴더</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>시카고컵스 vs 뉴욕양키스(오버 6.5) + 애슬레틱스 vs 디트로이트(언더 11.5)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.784</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MLB 3폴더</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>볼티모어 vs 필라델피아(오버 7.5) + 시애틀 vs 미네소타(오버 6.5) + LA에인절스 vs 밀워키(LA에인절스 +2.5) + LA다저스 vs 보스턴(보스턴 승) [실베팅시 보스턴 승 다리 추가]</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>10.0078</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>220170.72</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KBO/NPB 1폴더</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>두산 vs LG(오버 7.5) [NC vs KIA 경기취소로 단일 다리 정산]</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>74000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>126540</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>야쿠르트 vs 한신(언더 8.5) + 히로시마 vs 주니치(언더 7.5)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2.992</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>110704</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>kt vs 한화(오버 9.5) + 롯데 vs 삼성(언더 10.5) + 니혼햄 vs 지바롯데(지바롯데 승)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>4.6847</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NPB 단폴1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(오릭스 -2.5)</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>54750</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NPB 단폴2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(오릭스 승1패 2점차+)</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>39750</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MLB 1폴더</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>시애틀 vs 디트로이트(디트로이트 승1패 2점차+) + 텍사스 vs 샌프란시스코(샌프란시스코 +2.5)</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3.9615</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>237690</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MLB 2폴더</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>콜로라도 vs 탬파베이(언더 11.5) + 캔자스시티 vs 미네소타(캔자스시티 +2.5)</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2.324</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MLB 3폴더</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>시카고컵스 vs LA다저스(시카고컵스 +2.5) + 필라델피아 vs 워싱턴(워싱턴 +2.5) + 애틀랜타 vs 마이애미(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>54000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>4.0023</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NPB 1폴더</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(언더 7.5) + 소프트뱅크 vs 니혼햄(오버 6.5)</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3.009</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>120360</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>주니치 vs 야쿠르트(야쿠르트 승) + 지바롯데 vs 세이부(세이부 -2.5)</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>6.0356</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KBO/NPB 1폴더</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SSG vs LG(SSG +2.5) + 소프트뱅크 vs 니혼햄(오버 6.5)</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>106000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2.838</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>롯데 vs 키움(키움 승) + 주니치 vs 야쿠르트(야쿠르트 승)</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4.7089</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KBO/NPB 3폴더</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>히로시마 vs 요미우리(히로시마 승1패 2점차+) + 지바롯데 vs 세이부(세이부 -2.5) + 삼성 vs 한화(1점차)</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>28.2193</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NPB 2폴더</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>요코하마 vs 한신(요코하마 +2.5) + 소프트뱅크 vs 니혼햄(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>104000</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2.3711</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NPB 3폴더</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(라쿠텐 승) + 주니치 vs 야쿠르트(야쿠르트 승) + 히로시마 vs 요미우리(요미우리 승1패 2점차+)</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>10.8684</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한신 vs 주니치(오버 5.5) + 지바롯데 vs 오릭스(언더 8.5)</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>64000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2.9754</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>세이부 vs 소프트뱅크(세이부 승) + 니혼햄 vs 라쿠텐(언더 8.5)</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3.8402</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>요미우리 vs 야쿠르트(언더오버 오버 5.5) + 세이부 vs 소프트뱅크(세이부 승)</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3.097</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>161044</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한신 vs 주니치(주니치 승) + 니혼햄 vs 라쿠텐(라쿠텐 승)</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4.6098</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>221270.4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>필라델피아 vs 토론토(핸디캡 토론토 +2.5) + 워싱턴 vs 신시내티(언더 9.5)</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>49000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2.595</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>127155</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>밀워키 vs 미네소타(오버 8.5) + 애리조나 vs LA다저스(애리조나 승)</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3.8553</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>312279.3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>애리조나 vs LA다저스(핸디캡 애리조나 +2.5) + 텍사스 vs 볼티모어(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>106000</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2.5375</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>뉴욕양키스 vs 애틀랜타(오버 7.5) + 밀워키 vs 미네소타(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3.363</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>요코하마 vs 히로시마(핸디캡 히로시마 +2.5) + 한신 vs 주니치(주니치 승)</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>105000</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3.0573</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>니혼햄 vs 라쿠텐(라쿠텐 승) + 세이부 vs 소프트뱅크(세이부 승)</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>4.8438</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>밀워키 vs 미네소타(핸디캡 미네소타 +2.5) + 보스턴 vs 애슬레틱스(언더 10.5)</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>76000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2.715</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>206340</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>캔자스시티 vs 시카고컵스(언더 10.5) + 워싱턴 vs 신시내티(신시내티 승)</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>54000</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2.8044</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>애슬레틱스 vs 탬파베이(핸디캡 애슬레틱스 +2.5) + 샌디에이고 vs 밀워키(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2.6649</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 캔자스시티(핸디캡 캔자스시티 +2.5) + 미네소타 vs 볼티모어(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>98000</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2.8658</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>280848.4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 캔자스시티(핸디캡 캔자스시티 +2.5) + 미네소타 vs 볼티모어(미네소타 승)</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>샌프란시스코 vs 휴스턴(핸디캡 샌프란시스코 +2.5) + 마이애미 vs 피츠버그(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>94000</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2.9944</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>KIA vs 삼성(언더오버 오버 8.5) + 소프트뱅크 vs 지바롯데(핸디캡 지바롯데 +2.5)</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2.4613</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>주니치 vs 요코하마(승패 주니치 승) + 요미우리 vs 한신(언더오버 오버 5.5)</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2.9382</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>381966</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MLB 추가조합</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>애리조나 vs 콜로라도(콜로라도 승) + 샌프란시스코 vs 휴스턴(핸디캡 샌프란시스코 +2.5)</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3.5112</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>70224</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>세인트루이스 vs 필라델피아(핸디캡 세인트루이스 +2.5) + 디트로이트 vs 클리블랜드(오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2.3881</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>186271.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 캔자스시티(핸디캡 캔자스시티 +2.5) + 토론토 vs 보스턴(오버 6.5)</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2.3055</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>119886</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KIA vs 삼성(언더오버 오버 9.5) + 키움 vs LG(핸디캡 키움 +2.5)</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2.8552</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>두산 vs 한화(언더오버 오버 7.5) + SSG vs 롯데(언더오버 언더 10.5)</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KIA vs 삼성(핸디캡 KIA +2.5) + 두산 vs 한화(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2.5688</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>187522.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>소프트뱅크 vs 지바롯데(언더오버 오버 7.5) + 라쿠텐 vs 오릭스(언더오버 오버 6.5)</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.9928</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,497,000원</t>
+          <t>4,627,000원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-118,228원</t>
+          <t>-248,228원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1225,6 +1225,34 @@
       </c>
       <c r="H22" t="n">
         <v>0.8987699999999998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1276,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1356,25 +1384,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>2071000</v>
+        <v>2201000</v>
       </c>
       <c r="F4" t="n">
         <v>2032855.22</v>
       </c>
       <c r="G4" t="n">
-        <v>-38144.78000000003</v>
+        <v>-168144.78</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01841853211009176</v>
+        <v>-0.07639472058155385</v>
       </c>
     </row>
     <row r="5">
@@ -1891,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4946,66 +4974,132 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KBO/NPB 2폴더①</t>
+          <t>MLB 2폴더①</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KIA vs 삼성(핸디캡 KIA +2.5) + 두산 vs 한화(언더오버 오버 7.5)</t>
+          <t>LA에인절스 vs 텍사스(핸디캡 LA에인절스 +2.5) + 마이애미 vs 피츠버그(마이애미 승)</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2.5688</t>
+          <t>2.717</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>적중</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>187522.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>토론토 vs 보스턴(오버 7.5) + 미네소타 vs 필라델피아(미네소타 승)</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.9406</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>KIA vs 삼성(핸디캡 KIA +2.5) + 두산 vs 한화(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2.5688</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>187522.4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>KBO/NPB 2폴더②</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>소프트뱅크 vs 지바롯데(언더오버 오버 7.5) + 라쿠텐 vs 오릭스(언더오버 오버 6.5)</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D96" t="n">
         <v>57000</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>2.9928</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,627,000원</t>
+          <t>5,017,000원</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4,378,772원</t>
+          <t>4,953,459원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-248,228원</t>
+          <t>-63,541원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>881,772원</t>
+          <t>936,459원</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1234,25 +1234,53 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>257742</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2258</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.008684615384615384</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
         <v>2</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-130000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-1</v>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>260000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>316945.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>56945.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2190211538461538</v>
       </c>
     </row>
   </sheetData>
@@ -1272,10 +1300,10 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1356,25 +1384,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="E3" t="n">
-        <v>1490000</v>
+        <v>1750000</v>
       </c>
       <c r="F3" t="n">
-        <v>1303212.2</v>
+        <v>1843813.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-186787.8</v>
+        <v>93813.70000000019</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1253609395973155</v>
+        <v>0.05360782857142868</v>
       </c>
     </row>
     <row r="4">
@@ -1384,25 +1412,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="E4" t="n">
-        <v>2201000</v>
+        <v>2331000</v>
       </c>
       <c r="F4" t="n">
-        <v>2032855.22</v>
+        <v>2066941.22</v>
       </c>
       <c r="G4" t="n">
-        <v>-168144.78</v>
+        <v>-264058.78</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07639472058155385</v>
+        <v>-0.1132813299013299</v>
       </c>
     </row>
     <row r="5">
@@ -1472,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1908,6 +1936,44 @@
         <v>881771.8199999999</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>881771.8199999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>257742</v>
+      </c>
+      <c r="E23" t="n">
+        <v>879513.8199999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>879513.8199999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>260000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>316945.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>936459.3199999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1919,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5103,6 +5169,204 @@
         <v>0</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>오릭스 vs 니혼햄(승패 오릭스 승) + 롯데 vs NC(핸디캡 롯데 +2.5)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2.8638</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>257742</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>kt vs 키움(핸디캡 키움 +2.5) + LG vs SSG(핸디캡 SSG +2.5)</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2.5418</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>애틀랜타 vs 애리조나(핸디캡 애리조나 +2.5) + LA다저스 vs 밀워키(승패 밀워키 승)</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>117000</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3.321</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>피츠버그 vs 보스턴(핸디캡 피츠버그 +2.5) + 클리블랜드 vs 샌디에이고(승패 샌디에이고 승)</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>34086</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>야쿠르트 vs 요코하마(승패 야쿠르트 승) + 오릭스 vs 니혼햄(승패 오릭스 승)</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4.4485</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>소프트뱅크 vs 라쿠텐(승패 라쿠텐 승) + 히로시마 vs 한신(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>5.1429</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>282859.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,017,000원</t>
+          <t>5,147,000원</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4,953,459원</t>
+          <t>5,313,265원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-63,541원</t>
+          <t>166,265원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>936,459원</t>
+          <t>1,166,265원</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1281,6 +1281,34 @@
       </c>
       <c r="H24" t="n">
         <v>0.2190211538461538</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>359805.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>229805.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.767735384615384</v>
       </c>
     </row>
   </sheetData>
@@ -1303,7 +1331,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1412,25 +1440,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>2331000</v>
+        <v>2461000</v>
       </c>
       <c r="F4" t="n">
-        <v>2066941.22</v>
+        <v>2426746.82</v>
       </c>
       <c r="G4" t="n">
-        <v>-264058.78</v>
+        <v>-34253.18000000017</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1132813299013299</v>
+        <v>-0.01391839902478674</v>
       </c>
     </row>
     <row r="5">
@@ -1500,14 +1528,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1972,6 +2000,25 @@
       </c>
       <c r="E24" t="n">
         <v>936459.3199999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>936459.3199999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>359805.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1166264.92</v>
       </c>
     </row>
   </sheetData>
@@ -1985,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5367,6 +5414,72 @@
         <v>282859.5</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>뉴욕메츠 vs 워싱턴(핸디캡 워싱턴 +2.5) + 미네소타 vs 필라델피아(승패 미네소타 승)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2.3986</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>탬파베이 vs 볼티모어(언더오버 오버 7.5) + 애슬레틱스 vs 텍사스(언더오버 언더 10.5)</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2.9736</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>359805.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,147,000원</t>
+          <t>5,277,000원</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,313,265원</t>
+          <t>5,573,569원</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>166,265원</t>
+          <t>296,569원</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,166,265원</t>
+          <t>1,296,569원</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1309,6 +1309,34 @@
       </c>
       <c r="H25" t="n">
         <v>1.767735384615384</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>260304</v>
+      </c>
+      <c r="G26" t="n">
+        <v>130304</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.002338461538462</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1359,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1440,25 +1468,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.28</v>
       </c>
       <c r="E4" t="n">
-        <v>2461000</v>
+        <v>2591000</v>
       </c>
       <c r="F4" t="n">
-        <v>2426746.82</v>
+        <v>2687050.82</v>
       </c>
       <c r="G4" t="n">
-        <v>-34253.18000000017</v>
+        <v>96050.81999999983</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01391839902478674</v>
+        <v>0.03707094558085675</v>
       </c>
     </row>
     <row r="5">
@@ -1528,11 +1556,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2019,6 +2047,25 @@
       </c>
       <c r="E25" t="n">
         <v>1166264.92</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1166264.92</v>
+      </c>
+      <c r="C26" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>260304</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1296568.92</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5480,6 +5527,72 @@
         <v>359805.6</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>필라델피아 vs 마이애미(핸디캡 마이애미 +2.5) + 콜로라도 vs LA다저스(핸디캡 콜로라도 +2.5)</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2.625</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>탬파베이 vs 볼티모어(오버 7.5) + 시카고컵스 vs 시카고화이트삭스(오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3.2538</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>260304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="전체요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="일자별" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="리그별" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="잔고추이" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="베팅내역" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="신뢰도" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일자별" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="리그별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="잔고추이" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="베팅내역" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -486,7 +487,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +498,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,277,000원</t>
+          <t>5,547,000원</t>
         </is>
       </c>
     </row>
@@ -509,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,573,569원</t>
+          <t>5,855,378원</t>
         </is>
       </c>
     </row>
@@ -521,7 +522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>296,569원</t>
+          <t>308,378원</t>
         </is>
       </c>
     </row>
@@ -557,7 +558,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,296,569원</t>
+          <t>1,308,378원</t>
         </is>
       </c>
     </row>
@@ -569,7 +570,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -584,7 +585,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>표본 기간</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>표본 크기</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>109건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>최대 낙폭(MDD)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-93.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>최대 낙폭 구간</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1,065,080원 → 74,281원 (2026-07-31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ROI 95% 신뢰구간</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-27.9% ~ +38.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ROI가 0보다 크다고 말할 수 있는가</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>아니오 — 신뢰구간이 0을 포함해, 현재 표본으로는 운과 실력을 구분할 수 없습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>수익 상위 3일 순수익</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1,216,676원</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>상위 3일 제외 시 순수익</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-908,298원</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>상위일 날짜</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-08, 2026-08-11, 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1318,25 +1457,53 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
         <v>2</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0.5</v>
       </c>
       <c r="E26" t="n">
+        <v>270000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>542112.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>272112.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.007825185185185</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
         <v>130000</v>
       </c>
-      <c r="F26" t="n">
-        <v>260304</v>
-      </c>
-      <c r="G26" t="n">
-        <v>130304</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.002338461538462</v>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-130000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1344,7 +1511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1358,9 +1525,9 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1440,25 +1607,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="E3" t="n">
-        <v>1750000</v>
+        <v>1890000</v>
       </c>
       <c r="F3" t="n">
-        <v>1843813.7</v>
+        <v>2125622.5</v>
       </c>
       <c r="G3" t="n">
-        <v>93813.70000000019</v>
+        <v>235622.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05360782857142868</v>
+        <v>0.1246679894179894</v>
       </c>
     </row>
     <row r="4">
@@ -1468,25 +1635,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.28</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="E4" t="n">
-        <v>2591000</v>
+        <v>2721000</v>
       </c>
       <c r="F4" t="n">
         <v>2687050.82</v>
       </c>
       <c r="G4" t="n">
-        <v>96050.81999999983</v>
+        <v>-33949.18000000017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03707094558085675</v>
+        <v>-0.01247672914369723</v>
       </c>
     </row>
     <row r="5">
@@ -1550,13 +1717,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2059,13 +2226,32 @@
         <v>1166264.92</v>
       </c>
       <c r="C26" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>542112.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1438377.72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1438377.72</v>
+      </c>
+      <c r="C27" t="n">
         <v>130000</v>
       </c>
-      <c r="D26" t="n">
-        <v>260304</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1296568.92</v>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1308377.72</v>
       </c>
     </row>
   </sheetData>
@@ -2073,13 +2259,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5593,6 +5779,138 @@
         <v>260304</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>삼성 vs SSG(핸디캡 SSG+2.5) + 히로시마 vs 주니치(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>91000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3.0968</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>281808.8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>라쿠텐 vs 지바롯데(언더오버 오버 7.5) + 세이부 vs 오릭스(승패 오릭스 승)</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>49000</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>4.1748</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>클리블랜드 vs 샌프란시스코(핸디캡 샌프란시스코 +2.5) + 피츠버그 vs 디트로이트(승패 디트로이트 승)</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2.6989</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>필라델피아 vs 마이애미(핸디캡 마이애미 +2.5) + 시카고컵스 vs 시카고화이트삭스(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2.6224</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3,660,000원</t>
+          <t>3,795,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1,234,096원</t>
+          <t>1,099,096원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2,234,096원</t>
+          <t>2,099,096원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>109.9%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18일</t>
+          <t>19일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65건</t>
+          <t>67건</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.1% ~ +77.8%</t>
+          <t>-12.7% ~ +72.2%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17,420원</t>
+          <t>-117,580원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1430,6 +1430,34 @@
         <v>-130000</v>
       </c>
       <c r="H19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-135000</v>
+      </c>
+      <c r="H20" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1453,7 +1481,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1534,25 +1562,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.375</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E3" t="n">
-        <v>1840000</v>
+        <v>1975000</v>
       </c>
       <c r="F3" t="n">
         <v>2415060.82</v>
       </c>
       <c r="G3" t="n">
-        <v>575060.8199999998</v>
+        <v>440060.8199999998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.312533054347826</v>
+        <v>0.2228156050632911</v>
       </c>
     </row>
     <row r="4">
@@ -1594,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1973,6 +2001,25 @@
         <v>2234096.32</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2234096.32</v>
+      </c>
+      <c r="C20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2099096.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1984,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4048,6 +4095,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>콜로라도 vs LA다저스(핸디캡 콜로라도 +2.5) + 밀워키 vs 시애틀(승패 밀워키 승)</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>미네소타 vs 애틀랜타(승패 미네소타 승) + 시카고컵스 vs 시카고화이트삭스(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>67000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.3115</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3,795,000원</t>
+          <t>4,085,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1,099,096원</t>
+          <t>809,096원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2,099,096원</t>
+          <t>1,809,096원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67건</t>
+          <t>71건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,282,683원 → 1,022,683원 (2026-08-07)</t>
+          <t>2,364,096원 → 1,809,096원 (2026-08-20)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.7% ~ +72.2%</t>
+          <t>-20.2% ~ +62.1%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-117,580원</t>
+          <t>-407,580원</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>130000</v>
+        <v>260000</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-130000</v>
+        <v>-260000</v>
       </c>
       <c r="H19" t="n">
         <v>-1</v>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1449,13 +1449,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>135000</v>
+        <v>295000</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-135000</v>
+        <v>-295000</v>
       </c>
       <c r="H20" t="n">
         <v>-1</v>
@@ -1534,25 +1534,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.32</v>
       </c>
       <c r="E2" t="n">
-        <v>1230000</v>
+        <v>1520000</v>
       </c>
       <c r="F2" t="n">
         <v>1881861.1</v>
       </c>
       <c r="G2" t="n">
-        <v>651861.1000000001</v>
+        <v>361861.1000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5299683739837399</v>
+        <v>0.2380665131578948</v>
       </c>
     </row>
     <row r="3">
@@ -1992,13 +1992,13 @@
         <v>2364096.32</v>
       </c>
       <c r="C19" t="n">
-        <v>130000</v>
+        <v>260000</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2234096.32</v>
+        <v>2104096.32</v>
       </c>
     </row>
     <row r="20">
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2234096.32</v>
+        <v>2104096.32</v>
       </c>
       <c r="C20" t="n">
-        <v>135000</v>
+        <v>295000</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2099096.32</v>
+        <v>1809096.32</v>
       </c>
     </row>
   </sheetData>
@@ -2031,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4157,6 +4157,130 @@
         <v>0</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>삼성 vs SSG(핸디캡 SSG+2.5) + 히로시마 vs 주니치(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>93000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.8086</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한신 vs 야쿠르트(언더오버 오버 5.5) + 롯데 vs 키움(승패 롯데 승)</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.8552</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>세이부 vs 오릭스(언더오버 오버 6.5) + 히로시마 vs 주니치(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>111000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.7334</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한신 vs 야쿠르트(언더오버 오버 5.5) + 롯데 vs 키움(승패 롯데 승)</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>49000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.7556</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,085,000원</t>
+          <t>4,198,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4,894,096원</t>
+          <t>5,124,532원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>809,096원</t>
+          <t>926,532원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,809,096원</t>
+          <t>1,926,532원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>92.7%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19일</t>
+          <t>20일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71건</t>
+          <t>73건</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.2% ~ +62.1%</t>
+          <t>-16.9% ~ +63.1%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-407,580원</t>
+          <t>-290,144원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1459,6 +1459,34 @@
       </c>
       <c r="H20" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>113000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>230436</v>
+      </c>
+      <c r="G21" t="n">
+        <v>117436</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.039256637168142</v>
       </c>
     </row>
   </sheetData>
@@ -1534,25 +1562,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.32</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>1520000</v>
+        <v>1633000</v>
       </c>
       <c r="F2" t="n">
-        <v>1881861.1</v>
+        <v>2112297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>361861.1000000001</v>
+        <v>479297.1000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2380665131578948</v>
+        <v>0.2935071034905083</v>
       </c>
     </row>
     <row r="3">
@@ -1622,7 +1650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2048,25 @@
         <v>1809096.32</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1809096.32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>113000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>230436</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1926532.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2031,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4281,6 +4328,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화 vs LG(언더오버 오버 10.5) + 두산 vs 롯데(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>74000</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3.114</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>230436</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>키움 vs KIA(언더오버 오버 8.5) + 주니치 vs 야쿠르트(승패 야쿠르트 승)</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3.6714</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,198,000원</t>
+          <t>4,449,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,124,532원</t>
+          <t>5,348,839원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>926,532원</t>
+          <t>899,839원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,926,532원</t>
+          <t>1,899,839원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20일</t>
+          <t>22일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73건</t>
+          <t>77건</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.9% ~ +63.1%</t>
+          <t>-18.6% ~ +59.9%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-290,144원</t>
+          <t>-316,837원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1487,6 +1487,62 @@
       </c>
       <c r="H21" t="n">
         <v>1.039256637168142</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-96000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.7111111111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>116000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>185306.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>69306.79999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5974724137931033</v>
       </c>
     </row>
   </sheetData>
@@ -1506,9 +1562,9 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1562,25 +1618,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="E2" t="n">
-        <v>1633000</v>
+        <v>1768000</v>
       </c>
       <c r="F2" t="n">
-        <v>2112297.1</v>
+        <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>479297.1000000001</v>
+        <v>383297.1000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2935071034905083</v>
+        <v>0.2167970022624435</v>
       </c>
     </row>
     <row r="3">
@@ -1590,25 +1646,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="E3" t="n">
-        <v>1975000</v>
+        <v>2091000</v>
       </c>
       <c r="F3" t="n">
-        <v>2415060.82</v>
+        <v>2600367.62</v>
       </c>
       <c r="G3" t="n">
-        <v>440060.8199999998</v>
+        <v>509367.6199999996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2228156050632911</v>
+        <v>0.2436000095648014</v>
       </c>
     </row>
     <row r="4">
@@ -1650,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2123,44 @@
         <v>1926532.32</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1926532.32</v>
+      </c>
+      <c r="C22" t="n">
+        <v>135000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1830532.32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1830532.32</v>
+      </c>
+      <c r="C23" t="n">
+        <v>116000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>185306.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1899839.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2078,7 +2172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2086,7 +2180,7 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4390,6 +4484,130 @@
         <v>0</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>키움 vs KIA(언더오버 오버 7.5) [두산 vs 롯데 우천취소로 단일 다리 정산]</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>96000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>지바롯데 vs 니혼햄(승패 지바롯데 승) + 한화 vs LG(승패 한화 승) [둘 다 우천취소로 조합 전체 무효/전액환불]</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.9919</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>무효(전액환불)</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>시애틀 vs 시카고컵스(핸디캡 시카고컵스 +2.5) + 텍사스 vs LA에인절스(승패 LA에인절스 승)</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.7251</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>185306.8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>휴스턴 vs 애슬레틱스(핸디캡 애슬레틱스 +2.5) + 볼티모어 vs 탬파베이(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.3904</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,449,000원</t>
+          <t>4,818,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,348,839원</t>
+          <t>5,559,489원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>899,839원</t>
+          <t>741,489원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,899,839원</t>
+          <t>1,741,489원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22일</t>
+          <t>23일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77건</t>
+          <t>83건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 1,809,096원 (2026-08-20)</t>
+          <t>2,364,096원 → 1,741,489원 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.6% ~ +59.9%</t>
+          <t>-20.9% ~ +53.6%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-316,837원</t>
+          <t>-475,187원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1496,25 +1496,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E22" t="n">
-        <v>135000</v>
+        <v>244000</v>
       </c>
       <c r="F22" t="n">
-        <v>39000</v>
+        <v>107387.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-96000</v>
+        <v>-136612.8</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7111111111111111</v>
+        <v>-0.5598885245901639</v>
       </c>
     </row>
     <row r="23">
@@ -1524,25 +1524,53 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E23" t="n">
-        <v>116000</v>
+        <v>226000</v>
       </c>
       <c r="F23" t="n">
         <v>185306.8</v>
       </c>
       <c r="G23" t="n">
-        <v>69306.79999999999</v>
+        <v>-40693.20000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5974724137931033</v>
+        <v>-0.1800584070796461</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>142262.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-7737.600000000006</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.05158400000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1564,8 +1592,8 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1618,25 +1646,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="E2" t="n">
-        <v>1768000</v>
+        <v>1878000</v>
       </c>
       <c r="F2" t="n">
         <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>383297.1000000001</v>
+        <v>273297.1000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2167970022624435</v>
+        <v>0.1455256123535677</v>
       </c>
     </row>
     <row r="3">
@@ -1646,25 +1674,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.375</v>
       </c>
       <c r="E3" t="n">
-        <v>2091000</v>
+        <v>2350000</v>
       </c>
       <c r="F3" t="n">
-        <v>2600367.62</v>
+        <v>2811017.22</v>
       </c>
       <c r="G3" t="n">
-        <v>509367.6199999996</v>
+        <v>461017.2200000002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2436000095648014</v>
+        <v>0.196177540425532</v>
       </c>
     </row>
     <row r="4">
@@ -1706,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2133,13 +2161,13 @@
         <v>1926532.32</v>
       </c>
       <c r="C22" t="n">
-        <v>135000</v>
+        <v>244000</v>
       </c>
       <c r="D22" t="n">
-        <v>39000</v>
+        <v>107387.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1830532.32</v>
+        <v>1789919.52</v>
       </c>
     </row>
     <row r="23">
@@ -2149,16 +2177,35 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1830532.32</v>
+        <v>1789919.52</v>
       </c>
       <c r="C23" t="n">
-        <v>116000</v>
+        <v>226000</v>
       </c>
       <c r="D23" t="n">
         <v>185306.8</v>
       </c>
       <c r="E23" t="n">
-        <v>1899839.12</v>
+        <v>1749226.32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1749226.32</v>
+      </c>
+      <c r="C24" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>142262.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1741488.72</v>
       </c>
     </row>
   </sheetData>
@@ -2172,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4608,6 +4655,192 @@
         <v>0</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>두산 vs 롯데(언더오버 오버 7.5) + 키움 vs KIA(핸디캡 키움 +2.5)</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>53000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3.0096</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>소프트뱅크 vs 오릭스(언더오버 오버 7.5) + 지바롯데 vs 니혼햄(승패 지바롯데 승)</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3.4762</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LA다저스 vs 피츠버그(핸디캡 피츠버그 +2.5) + 밀워키 vs 애틀랜타(언더오버 오버 6.5)</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>81000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>뉴욕양키스 vs 토론토(핸디캡 토론토 +2.5) + 시애틀 vs 시카고컵스(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.4424</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>68387.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>콜로라도 vs 클리블랜드(핸디캡 콜로라도 +2.5) + LA다저스 vs 피츠버그(핸디캡 피츠버그 +2.5)</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>94000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.4168</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>보스턴 vs 샌프란시스코(핸디캡 샌프란시스코 +2.5) + 시애틀 vs 시카고컵스(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>56000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.5404</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>142262.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4,818,000원</t>
+          <t>5,044,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>741,489원</t>
+          <t>515,489원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,741,489원</t>
+          <t>1,515,489원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23일</t>
+          <t>25일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83건</t>
+          <t>87건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-35.9%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 1,741,489원 (2026-08-24)</t>
+          <t>2,364,096원 → 1,515,489원 (2026-08-26)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9% ~ +53.6%</t>
+          <t>-24.5% ~ +46.1%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-475,187원</t>
+          <t>-701,187원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1571,6 +1571,62 @@
       </c>
       <c r="H24" t="n">
         <v>-0.05158400000000004</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>105000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-105000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-121000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1674,25 +1730,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.375</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="E3" t="n">
-        <v>2350000</v>
+        <v>2576000</v>
       </c>
       <c r="F3" t="n">
         <v>2811017.22</v>
       </c>
       <c r="G3" t="n">
-        <v>461017.2200000002</v>
+        <v>235017.2200000002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.196177540425532</v>
+        <v>0.09123339285714294</v>
       </c>
     </row>
     <row r="4">
@@ -1734,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2208,6 +2264,44 @@
         <v>1741488.72</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1741488.72</v>
+      </c>
+      <c r="C25" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1636488.72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1636488.72</v>
+      </c>
+      <c r="C26" t="n">
+        <v>121000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1515488.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2219,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4841,6 +4935,130 @@
         <v>142262.4</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>시애틀 vs 필라델피아(언더오버 오버 6.5) + 디트로이트 vs 탬파베이(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.9929</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>마이애미 vs 보스턴(승패 마이애미 승) + 워싱턴 vs 콜로라도(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>시애틀 vs 필라델피아(핸디캡 필라델피아 +2.5) + 애틀랜타 vs LA다저스(승패 애틀랜타 승)</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>87000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.6061</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>디트로이트 vs 탬파베이(언더오버 오버 7.5) + 워싱턴 vs 콜로라도(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.9058</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,044,000원</t>
+          <t>5,311,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>515,489원</t>
+          <t>248,489원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,515,489원</t>
+          <t>1,248,489원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87건</t>
+          <t>91건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-47.2%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 1,515,489원 (2026-08-26)</t>
+          <t>2,364,096원 → 1,248,489원 (2026-08-26)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5% ~ +46.1%</t>
+          <t>-28.6% ~ +39.6%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-701,187원</t>
+          <t>-968,187원</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>105000</v>
+        <v>234000</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-105000</v>
+        <v>-234000</v>
       </c>
       <c r="H25" t="n">
         <v>-1</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>121000</v>
+        <v>259000</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-121000</v>
+        <v>-259000</v>
       </c>
       <c r="H26" t="n">
         <v>-1</v>
@@ -1650,7 +1650,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1702,25 +1702,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>1878000</v>
+        <v>2145000</v>
       </c>
       <c r="F2" t="n">
         <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>273297.1000000001</v>
+        <v>6297.100000000093</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1455256123535677</v>
+        <v>0.002935710955710999</v>
       </c>
     </row>
     <row r="3">
@@ -2274,13 +2274,13 @@
         <v>1741488.72</v>
       </c>
       <c r="C25" t="n">
-        <v>105000</v>
+        <v>234000</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1636488.72</v>
+        <v>1507488.72</v>
       </c>
     </row>
     <row r="26">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1636488.72</v>
+        <v>1507488.72</v>
       </c>
       <c r="C26" t="n">
-        <v>121000</v>
+        <v>259000</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1515488.72</v>
+        <v>1248488.72</v>
       </c>
     </row>
   </sheetData>
@@ -2313,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5059,6 +5059,130 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(언더오버 오버 6.5) + 키움 vs 삼성(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>87000</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3.0051</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LG vs NC(언더오버 오버 8.5) + 세이부 vs 니혼햄(언더오버 오버 5.5)</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.8875</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>오릭스 vs 라쿠텐(승1패 라쿠텐 2점차+) + 주니치 vs 한신(승패 주니치 승)</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4.5668</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>히로시마 vs 요코하마(승패 히로시마 승) + 야쿠르트 vs 요미우리(승패 야쿠르트 승)</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5.6166</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,311,000원</t>
+          <t>5,392,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>248,489원</t>
+          <t>167,489원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,248,489원</t>
+          <t>1,167,489원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25일</t>
+          <t>26일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91건</t>
+          <t>93건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-50.6%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 1,248,489원 (2026-08-26)</t>
+          <t>2,364,096원 → 1,167,489원 (2026-08-27)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.6% ~ +39.6%</t>
+          <t>-29.6% ~ +37.8%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-968,187원</t>
+          <t>-1,049,187원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1626,6 +1626,34 @@
         <v>-259000</v>
       </c>
       <c r="H26" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-81000</v>
+      </c>
+      <c r="H27" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1646,7 +1674,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -1702,25 +1730,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.2432432432432433</v>
       </c>
       <c r="E2" t="n">
-        <v>2145000</v>
+        <v>2226000</v>
       </c>
       <c r="F2" t="n">
         <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>6297.100000000093</v>
+        <v>-74702.89999999991</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002935710955710999</v>
+        <v>-0.0335592542677448</v>
       </c>
     </row>
     <row r="3">
@@ -1790,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2302,6 +2330,25 @@
         <v>1248488.72</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1248488.72</v>
+      </c>
+      <c r="C27" t="n">
+        <v>81000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1167488.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2313,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5183,6 +5230,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SSG vs 한화(핸디캡 SSG +2.5) + 주니치 vs 한신(승패 주니치 승)</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>히로시마 vs 요코하마(승패 히로시마 승) + 지바롯데 vs 소프트뱅크(승패 지바롯데 승)</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.1977</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,392,000원</t>
+          <t>5,660,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>167,489원</t>
+          <t>-100,511원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,167,489원</t>
+          <t>899,489원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>-10.1%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26일</t>
+          <t>27일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93건</t>
+          <t>99건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-62.0%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 1,167,489원 (2026-08-27)</t>
+          <t>2,364,096원 → 899,489원 (2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6% ~ +37.8%</t>
+          <t>-32.5% ~ +32.3%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1,049,187원</t>
+          <t>-1,317,187원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1645,15 +1645,43 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>81000</v>
+        <v>200000</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-81000</v>
+        <v>-200000</v>
       </c>
       <c r="H27" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>149000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-149000</v>
+      </c>
+      <c r="H28" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -1677,8 +1705,8 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1730,25 +1758,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2432432432432433</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="E2" t="n">
-        <v>2226000</v>
+        <v>2300000</v>
       </c>
       <c r="F2" t="n">
         <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-74702.89999999991</v>
+        <v>-148702.8999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0335592542677448</v>
+        <v>-0.06465343478260865</v>
       </c>
     </row>
     <row r="3">
@@ -1758,25 +1786,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3125</v>
       </c>
       <c r="E3" t="n">
-        <v>2576000</v>
+        <v>2770000</v>
       </c>
       <c r="F3" t="n">
         <v>2811017.22</v>
       </c>
       <c r="G3" t="n">
-        <v>235017.2200000002</v>
+        <v>41017.2200000002</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09123339285714294</v>
+        <v>0.01480766064981957</v>
       </c>
     </row>
     <row r="4">
@@ -1818,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2340,13 +2368,32 @@
         <v>1248488.72</v>
       </c>
       <c r="C27" t="n">
-        <v>81000</v>
+        <v>200000</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1167488.72</v>
+        <v>1048488.72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1048488.72</v>
+      </c>
+      <c r="C28" t="n">
+        <v>149000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>899488.72</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5292,6 +5339,192 @@
         <v>0</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>롯데 vs LG(승패 롯데 승, 경기취소로 다리 무효) + 오릭스 vs 소프트뱅크(승패 오릭스 승)</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4.4844</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>요코하마 vs 주니치(승패 주니치 승) + 니혼햄 vs 지바롯데(승패 지바롯데 승)</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>5.3584</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>애슬레틱스 vs 미네소타(핸디캡 애슬레틱스 +2.5) + 시애틀 vs 필라델피아(승패 시애틀 승)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>71000</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>샌프란시스코 vs 신시내티(승패 샌프란시스코 승) + 세인트루이스 vs 볼티모어(승패 볼티모어 승)</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3.078</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>뉴욕메츠 vs 밀워키(핸디캡 뉴욕메츠 +2.5) + 애틀랜타 vs LA다저스(승패 애틀랜타 승)</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.7825</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>샌프란시스코 vs 애리조나(승패 애리조나 승) + 토론토 vs 캔자스시티(승1패 캔자스시티 2점차+)</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3.774</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,660,000원</t>
+          <t>5,812,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,559,489원</t>
+          <t>5,652,191원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-100,511원</t>
+          <t>-159,809원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>899,489원</t>
+          <t>840,191원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27일</t>
+          <t>28일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99건</t>
+          <t>103건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-62.0%</t>
+          <t>-64.5%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 899,489원 (2026-08-28)</t>
+          <t>2,364,096원 → 840,191원 (2026-08-29)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.5% ~ +32.3%</t>
+          <t>-33.5% ~ +30.3%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1,317,187원</t>
+          <t>-1,376,485원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1683,6 +1683,34 @@
       </c>
       <c r="H28" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E29" t="n">
+        <v>152000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>92702.39999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-59297.60000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.3901157894736842</v>
       </c>
     </row>
   </sheetData>
@@ -1758,25 +1786,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="E2" t="n">
-        <v>2300000</v>
+        <v>2366000</v>
       </c>
       <c r="F2" t="n">
         <v>2151297.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-148702.8999999999</v>
+        <v>-214702.8999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06465343478260865</v>
+        <v>-0.09074509721048178</v>
       </c>
     </row>
     <row r="3">
@@ -1786,25 +1814,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3125</v>
+        <v>0.32</v>
       </c>
       <c r="E3" t="n">
-        <v>2770000</v>
+        <v>2856000</v>
       </c>
       <c r="F3" t="n">
-        <v>2811017.22</v>
+        <v>2903719.62</v>
       </c>
       <c r="G3" t="n">
-        <v>41017.2200000002</v>
+        <v>47719.62000000011</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01480766064981957</v>
+        <v>0.01670855042016811</v>
       </c>
     </row>
     <row r="4">
@@ -1846,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2396,6 +2424,25 @@
         <v>899488.72</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>899488.72</v>
+      </c>
+      <c r="C29" t="n">
+        <v>152000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>92702.39999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>840191.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2407,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5525,6 +5572,130 @@
         <v>0</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>히로시마 vs 야쿠르트(승패 히로시마 승) + 한화 vs NC(언더오버 오버 9.5)</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3.192</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>두산 vs 키움(언더오버 오버 7.5) + 롯데 vs LG(승패 롯데 승)</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>47000</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4.0257</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>디트로이트 vs LA다저스(핸디캡 디트로이트 +2.5) + 세인트루이스 vs 피츠버그(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.852</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>탬파베이 vs 샌디에이고(언더오버 오버 7.5) + 미네소타 vs 시카고화이트삭스(승패 시카고화이트삭스 승)</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3.3108</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>92702.39999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5,812,000원</t>
+          <t>6,114,000원</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,652,191원</t>
+          <t>5,906,912원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-159,809원</t>
+          <t>-207,088원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>840,191원</t>
+          <t>792,912원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-20.7%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28일</t>
+          <t>32일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103건</t>
+          <t>115건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-64.5%</t>
+          <t>-67.5%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 840,191원 (2026-08-29)</t>
+          <t>2,364,096원 → 767,191원 (2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.5% ~ +30.3%</t>
+          <t>-33.4% ~ +26.5%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1,376,485원</t>
+          <t>-1,423,764원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1711,6 +1711,118 @@
       </c>
       <c r="H29" t="n">
         <v>-0.3901157894736842</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>51000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>29000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.4313725490196079</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>51000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>101000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>140842.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39842.79999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3944831683168316</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E33" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>84878</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-14122</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.1426464646464647</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1846,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1786,25 +1898,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.2127659574468085</v>
       </c>
       <c r="E2" t="n">
-        <v>2366000</v>
+        <v>2519000</v>
       </c>
       <c r="F2" t="n">
-        <v>2151297.1</v>
+        <v>2321139.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-214702.8999999999</v>
+        <v>-197860.1000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09074509721048178</v>
+        <v>-0.07854708217546649</v>
       </c>
     </row>
     <row r="3">
@@ -1814,25 +1926,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>0.32</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="E3" t="n">
-        <v>2856000</v>
+        <v>3005000</v>
       </c>
       <c r="F3" t="n">
-        <v>2903719.62</v>
+        <v>2988597.62</v>
       </c>
       <c r="G3" t="n">
-        <v>47719.62000000011</v>
+        <v>-16402.37999999989</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01670855042016811</v>
+        <v>-0.005458362728785321</v>
       </c>
     </row>
     <row r="4">
@@ -1874,7 +1986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2443,6 +2555,82 @@
         <v>840191.12</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>840191.12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>51000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>818191.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>818191.12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>51000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>767191.12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>767191.12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>101000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>140842.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>807033.9199999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>807033.9199999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>99000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>84878</v>
+      </c>
+      <c r="E33" t="n">
+        <v>792911.9199999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2454,7 +2642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5696,6 +5884,378 @@
         <v>92702.39999999999</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>요코하마 vs 주니치(핸디캡 주니치 +2.5) + 오릭스 vs 소프트뱅크(승패 오릭스 승)</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.6703</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>롯데 vs LG(핸디캡 롯데 +2.5) + KIA vs SSG(언더오버 오버 8.5) [둘 다 경기취소로 조합 전체 무효/전액환불]</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>29000</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.5102</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>무효(전액환불)</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>디트로이트 vs LA다저스(핸디캡 디트로이트 +2.5) + 미네소타 vs 시카고화이트삭스(승패 시카고화이트삭스 승)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>LA에인절스 vs 필라델피아(핸디캡 LA에인절스 +2.5) + 워싱턴 vs 마이애미(승패 워싱턴 승)</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>두산 vs LG(언더오버 오버 8.5) + 주니치 vs 히로시마(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.5904</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>지바롯데 vs 세이부(승패 지바롯데 승) + 니혼햄 vs 소프트뱅크(승패 니혼햄 승)</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E110" t="n">
+        <v>5.0301</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>140842.8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>텍사스 vs 애슬레틱스(언더오버 오버 7.5) + 휴스턴 vs 시카고화이트삭스(승패 시카고화이트삭스 승)</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.4161</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>탬파베이 vs 뉴욕메츠(승패 뉴욕메츠 승) + 미네소타 vs 디트로이트(승패 디트로이트 승)</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4.5571</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MLB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>워싱턴 vs 애틀랜타(핸디캡 워싱턴 +2.5) + 텍사스 vs 애슬레틱스(언더오버 오버 7.5)</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>31000</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.738</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>적중</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>84878</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MLB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>탬파베이 vs 뉴욕메츠(언더오버 오버 7.5) + 캔자스시티 vs 마이애미(승패 캔자스시티 승)</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.8724</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>키움 vs SSG(언더오버 오버 8.5) + 니혼햄 vs 소프트뱅크(승패 니혼햄 승)</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.2725</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>야쿠르트 vs 한신(언더오버 언더 7.5) + 주니치 vs 히로시마(승패 히로시마 승)</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3.8192</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Track_Record.xlsx
+++ b/data/Track_Record.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6,114,000원</t>
+          <t>6,162,000원</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-207,088원</t>
+          <t>-255,088원</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>792,912원</t>
+          <t>744,912원</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-25.5%</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32일</t>
+          <t>33일</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115건</t>
+          <t>117건</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,364,096원 → 767,191원 (2026-08-31)</t>
+          <t>2,364,096원 → 744,912원 (2026-09-03)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.4% ~ +26.5%</t>
+          <t>-33.8% ~ +26.5%</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-1,423,764원</t>
+          <t>-1,471,764원</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1823,6 +1823,34 @@
       </c>
       <c r="H33" t="n">
         <v>-0.1426464646464647</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-48000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1844,8 +1872,8 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1898,25 +1926,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="E2" t="n">
-        <v>2519000</v>
+        <v>2567000</v>
       </c>
       <c r="F2" t="n">
         <v>2321139.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-197860.1000000001</v>
+        <v>-245860.0999999996</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07854708217546649</v>
+        <v>-0.09577721075185026</v>
       </c>
     </row>
     <row r="3">
@@ -1986,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2659,25 @@
         <v>792911.9199999999</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>792911.9199999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>744911.9199999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2642,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6256,6 +6303,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더①</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>야쿠르트 vs 한신(핸디캡 야쿠르트 +2.5) + 키움 vs SSG(언더오버 오버 8.5)</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>31000</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.5578</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KBO/NPB 2폴더②</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>주니치 vs 히로시마(승패 주니치 승) + NC vs KIA(승패 NC 승) [NC vs KIA는 경기취소로 다리 무효]</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.6218</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
